--- a/artfynd/A 42195-2024 artfynd.xlsx
+++ b/artfynd/A 42195-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128937600</v>
       </c>
       <c r="B2" t="n">
-        <v>92798</v>
+        <v>92802</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 42195-2024 artfynd.xlsx
+++ b/artfynd/A 42195-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128937600</v>
       </c>
       <c r="B2" t="n">
-        <v>92802</v>
+        <v>92807</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 42195-2024 artfynd.xlsx
+++ b/artfynd/A 42195-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128937600</v>
       </c>
       <c r="B2" t="n">
-        <v>92815</v>
+        <v>92820</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 42195-2024 artfynd.xlsx
+++ b/artfynd/A 42195-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128937600</v>
       </c>
       <c r="B2" t="n">
-        <v>92820</v>
+        <v>92823</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 42195-2024 artfynd.xlsx
+++ b/artfynd/A 42195-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -774,6 +774,128 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>129224521</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57720</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>753587</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7093251</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>Tallhögstubbe</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Tallhögstubbe</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 42195-2024 artfynd.xlsx
+++ b/artfynd/A 42195-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128937600</v>
       </c>
       <c r="B2" t="n">
-        <v>92823</v>
+        <v>92830</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>129224521</v>
       </c>
       <c r="B3" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 42195-2024 artfynd.xlsx
+++ b/artfynd/A 42195-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128937600</v>
       </c>
       <c r="B2" t="n">
-        <v>92830</v>
+        <v>92837</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 42195-2024 artfynd.xlsx
+++ b/artfynd/A 42195-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128937600</v>
       </c>
       <c r="B2" t="n">
-        <v>92837</v>
+        <v>92839</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>129224521</v>
       </c>
       <c r="B3" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 42195-2024 artfynd.xlsx
+++ b/artfynd/A 42195-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128937600</v>
       </c>
       <c r="B2" t="n">
-        <v>92839</v>
+        <v>92825</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 42195-2024 artfynd.xlsx
+++ b/artfynd/A 42195-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128937600</v>
       </c>
       <c r="B2" t="n">
-        <v>92825</v>
+        <v>92826</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 42195-2024 artfynd.xlsx
+++ b/artfynd/A 42195-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128937600</v>
       </c>
       <c r="B2" t="n">
-        <v>92826</v>
+        <v>92829</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 42195-2024 artfynd.xlsx
+++ b/artfynd/A 42195-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>128937600</v>
       </c>
       <c r="B2" t="n">
-        <v>92836</v>
+        <v>93201</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -777,50 +777,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129224521</v>
+        <v>129224530</v>
       </c>
       <c r="B3" t="n">
-        <v>57727</v>
+        <v>93201</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>4365</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>753587</v>
+        <v>753557</v>
       </c>
       <c r="R3" t="n">
-        <v>7093251</v>
+        <v>7093155</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -855,6 +850,11 @@
           <t>2025-10-19</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Kapad tallåga</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -864,26 +864,6 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>Tallhögstubbe</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Tallhögstubbe</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
@@ -896,6 +876,234 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129224533</v>
+      </c>
+      <c r="B4" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>753632</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7093270</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Vid stig</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129224521</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>753587</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7093251</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>Tallhögstubbe</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Tallhögstubbe</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 42195-2024 artfynd.xlsx
+++ b/artfynd/A 42195-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128937600</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129224530</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -982,6 +997,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129224533</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1104,8 +1124,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129224521</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>